--- a/results/naturverbundenheit/base_data/nature-dataset_explainable_scaling_factors.xlsx
+++ b/results/naturverbundenheit/base_data/nature-dataset_explainable_scaling_factors.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6520000</v>
+        <v>652000000</v>
       </c>
     </row>
     <row r="9">
